--- a/outputs/evaluation/decision/v2/CF_M05/run_2/CF_M05_decision_eval_llm_report.xlsx
+++ b/outputs/evaluation/decision/v2/CF_M05/run_2/CF_M05_decision_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,100 +471,210 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AD_04</t>
+          <t>AD_03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Angular applies the MVVM pattern, as its architecture is based on components and services.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
+          <t>This microservice has the main function of routing all communications to the corresponding microservice within the system architecture.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P_03</t>
+          <t>AU_08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>MVVM</t>
-        </is>
-      </c>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>MVVM</t>
+          <t>Leader Service</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CF_M05_AD10</t>
+          <t>CF_M05_AD04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+          <t>This microservice is essential for maintaining data confidentiality and protection.</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6804</v>
+        <v>0.7113</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AD_05</t>
+          <t>AD_04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>The portal microservice incorporates the binaries necessary for the frontEnd [...] of the rest of the applications of the portal. This ensures that the presentation layer is available and updated, facilitating deployment and reducing dependence on external elements.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AU_09</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Portal Service</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CF_M05_AD03</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>the portal not only centralizes access, but also ensures the visual and functional coherence of the entire ecosystem.</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7473</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD_07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>This microservice has as its main function the planning and programming of processes within the system.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AU_12</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scheduler Service</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CF_M05_AD01</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Each microservice is deployed independently, which allows updates, scaling and maintenance without affecting the rest of the system. It also allows each service to have its own programming language, database and environment. This flexibility facilitates adaptation to change and scalability of the application and improves the resilience of the system, since an error in a microservice does not mean the complete collapse of the application.</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>0.6771</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD_09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Angular applies the MVVM (Model-View-ViewModel) pattern, as its architecture is based on components and services.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>P_03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>MVVM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CF_M05_AD10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>When making the decision to use Angular for frontEnd development and Spring for the backEnd, several technological criteria were considered, the work methodology that would be implemented throughout the development of the application was thought about and the long-term maintainability of the project was taken into consideration.</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD_10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Spring Boot organizes the code following the layered pattern with which responsibilities are separated.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>P_04</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
         <is>
           <t>Layered Architecture</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Layered Architecture</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Layered Architecture</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>CF_M05_AD12</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>This structure clarifies roles, avoids unnecessary coupling, and makes it easier to test, reuse, and maintain the code over time.</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J6" t="n">
         <v>0.7287</v>
       </c>
     </row>
